--- a/students/بیاتhip4.1ok.xlsx
+++ b/students/بیاتhip4.1ok.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206C17AC-D59D-4968-8D7F-A65B09FCEC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>شماره پرونده</t>
   </si>
@@ -61,9 +62,6 @@
   </si>
   <si>
     <t>ارمیلا</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">سیدحسین </t>
@@ -87,12 +85,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -143,11 +141,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,20 +417,20 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="41.42578125" customWidth="1"/>
+    <col min="5" max="6" width="12.09765625" customWidth="1"/>
+    <col min="7" max="7" width="41.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -471,7 +468,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1">
         <v>9196995686</v>
@@ -480,7 +477,6 @@
         <v>9100362339</v>
       </c>
       <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
@@ -493,7 +489,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1">
         <v>9377348749</v>
@@ -502,7 +498,6 @@
         <v>9119960494</v>
       </c>
       <c r="G3" s="1"/>
-      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -515,7 +510,7 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1">
         <v>9192419611</v>
@@ -524,7 +519,6 @@
         <v>9102022806</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -537,13 +531,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>9192419611</v>
+      </c>
+      <c r="F5" s="1">
+        <v>9102022806</v>
       </c>
       <c r="G5" s="1"/>
     </row>
@@ -552,13 +546,13 @@
         <v>111173</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
         <v>9102411087</v>
@@ -569,42 +563,42 @@
       <c r="G6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+      <c r="A7" s="2">
         <v>111166</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2">
+        <v>9011557299</v>
+      </c>
+      <c r="F7" s="2">
+        <v>9193176986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>111173</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="3">
-        <v>9011557299</v>
-      </c>
-      <c r="F7" s="3">
-        <v>9193176986</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>111173</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>9147646841</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>9909650194</v>
       </c>
     </row>
